--- a/automation/reports/Excel/Selenium_Testing_Report.xlsx
+++ b/automation/reports/Excel/Selenium_Testing_Report.xlsx
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Execution Timestamp: 2026-07-30 22:30:30 UTC</t>
+          <t>Execution Timestamp: 2026-07-30 22:50:22 UTC</t>
         </is>
       </c>
     </row>

--- a/automation/reports/Excel/Selenium_Testing_Report.xlsx
+++ b/automation/reports/Excel/Selenium_Testing_Report.xlsx
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Execution Timestamp: 2026-07-30 22:50:22 UTC</t>
+          <t>Execution Timestamp: 2026-07-30 22:57:08 UTC</t>
         </is>
       </c>
     </row>
